--- a/Flujo de Efectivo/Flujo de efectivo.xlsx
+++ b/Flujo de Efectivo/Flujo de efectivo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Flujo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Flujo de Efectivo/Flujo de efectivo.xlsx
+++ b/Flujo de Efectivo/Flujo de efectivo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Flujo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="003D5A28"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="13"/>
     </font>
   </fonts>
@@ -46,17 +51,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="003D5A28"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="00EEF3E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009DC3E6"/>
+        <fgColor rgb="005B7F3B"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,16 +94,16 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE36"/>
+  <dimension ref="A1:AF36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -500,6 +505,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="18" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -658,6 +664,11 @@
           <t>25-30 mayo</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>03-08 julio 2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -755,6 +766,9 @@
       <c r="AE2" s="3" t="n">
         <v>-5379</v>
       </c>
+      <c r="AF2" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -852,6 +866,9 @@
       <c r="AE3" s="3" t="n">
         <v>-54740.4</v>
       </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -949,6 +966,9 @@
       <c r="AE4" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF4" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1046,6 +1066,9 @@
       <c r="AE5" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF5" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1143,6 +1166,9 @@
       <c r="AE6" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF6" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1240,6 +1266,9 @@
       <c r="AE7" s="3" t="n">
         <v>-4172.11</v>
       </c>
+      <c r="AF7" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1337,6 +1366,9 @@
       <c r="AE8" s="3" t="n">
         <v>-3500</v>
       </c>
+      <c r="AF8" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1434,6 +1466,9 @@
       <c r="AE9" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF9" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1531,6 +1566,9 @@
       <c r="AE10" s="3" t="n">
         <v>-4750</v>
       </c>
+      <c r="AF10" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1628,6 +1666,9 @@
       <c r="AE11" s="3" t="n">
         <v>-13091.4</v>
       </c>
+      <c r="AF11" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1725,6 +1766,9 @@
       <c r="AE12" s="3" t="n">
         <v>-13428</v>
       </c>
+      <c r="AF12" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1822,6 +1866,9 @@
       <c r="AE13" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF13" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1919,6 +1966,9 @@
       <c r="AE14" s="3" t="n">
         <v>-11000</v>
       </c>
+      <c r="AF14" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2016,6 +2066,9 @@
       <c r="AE15" s="3" t="n">
         <v>-6086.26</v>
       </c>
+      <c r="AF15" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2113,6 +2166,9 @@
       <c r="AE16" s="3" t="n">
         <v>-20000</v>
       </c>
+      <c r="AF16" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2210,6 +2266,9 @@
       <c r="AE17" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF17" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2307,6 +2366,9 @@
       <c r="AE18" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF18" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2404,6 +2466,9 @@
       <c r="AE19" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF19" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2501,6 +2566,9 @@
       <c r="AE20" s="3" t="n">
         <v>-151750</v>
       </c>
+      <c r="AF20" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2598,6 +2666,9 @@
       <c r="AE21" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF21" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2695,6 +2766,9 @@
       <c r="AE22" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF22" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2792,6 +2866,9 @@
       <c r="AE23" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF23" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2889,6 +2966,9 @@
       <c r="AE24" s="3" t="n">
         <v>-10000</v>
       </c>
+      <c r="AF24" s="3" t="n">
+        <v>-20000</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2986,6 +3066,9 @@
       <c r="AE25" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF25" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3083,6 +3166,9 @@
       <c r="AE26" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF26" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3180,6 +3266,9 @@
       <c r="AE27" s="3" t="n">
         <v>-26453.74</v>
       </c>
+      <c r="AF27" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3277,6 +3366,9 @@
       <c r="AE28" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF28" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3374,6 +3466,9 @@
       <c r="AE29" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF29" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3471,6 +3566,9 @@
       <c r="AE30" s="3" t="n">
         <v>-15370</v>
       </c>
+      <c r="AF30" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3568,6 +3666,9 @@
       <c r="AE31" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF31" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3665,6 +3766,9 @@
       <c r="AE32" s="3" t="n">
         <v>311700</v>
       </c>
+      <c r="AF32" s="3" t="n">
+        <v>1100</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3762,6 +3866,9 @@
       <c r="AE33" s="5" t="n">
         <v>311700</v>
       </c>
+      <c r="AF33" s="5" t="n">
+        <v>1100</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3859,6 +3966,9 @@
       <c r="AE34" s="5" t="n">
         <v>-339720.91</v>
       </c>
+      <c r="AF34" s="5" t="n">
+        <v>-20000</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -3956,6 +4066,9 @@
       <c r="AE35" s="7" t="n">
         <v>-28020.91</v>
       </c>
+      <c r="AF35" s="7" t="n">
+        <v>-18900</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -4052,6 +4165,9 @@
       </c>
       <c r="AE36" s="5" t="n">
         <v>-118369.68</v>
+      </c>
+      <c r="AF36" s="5" t="n">
+        <v>-137269.68</v>
       </c>
     </row>
   </sheetData>

--- a/Flujo de Efectivo/Flujo de efectivo.xlsx
+++ b/Flujo de Efectivo/Flujo de efectivo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Flujo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF36"/>
+  <dimension ref="A1:AE36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,6 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="18" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -664,11 +663,6 @@
           <t>25-30 mayo</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>03-08 julio 2026</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -766,9 +760,6 @@
       <c r="AE2" s="3" t="n">
         <v>-5379</v>
       </c>
-      <c r="AF2" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -866,9 +857,6 @@
       <c r="AE3" s="3" t="n">
         <v>-54740.4</v>
       </c>
-      <c r="AF3" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -966,9 +954,6 @@
       <c r="AE4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF4" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1066,9 +1051,6 @@
       <c r="AE5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF5" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1166,9 +1148,6 @@
       <c r="AE6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF6" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1266,9 +1245,6 @@
       <c r="AE7" s="3" t="n">
         <v>-4172.11</v>
       </c>
-      <c r="AF7" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1366,9 +1342,6 @@
       <c r="AE8" s="3" t="n">
         <v>-3500</v>
       </c>
-      <c r="AF8" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1466,9 +1439,6 @@
       <c r="AE9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF9" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1566,9 +1536,6 @@
       <c r="AE10" s="3" t="n">
         <v>-4750</v>
       </c>
-      <c r="AF10" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1666,9 +1633,6 @@
       <c r="AE11" s="3" t="n">
         <v>-13091.4</v>
       </c>
-      <c r="AF11" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1766,9 +1730,6 @@
       <c r="AE12" s="3" t="n">
         <v>-13428</v>
       </c>
-      <c r="AF12" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1866,9 +1827,6 @@
       <c r="AE13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF13" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1966,9 +1924,6 @@
       <c r="AE14" s="3" t="n">
         <v>-11000</v>
       </c>
-      <c r="AF14" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2066,9 +2021,6 @@
       <c r="AE15" s="3" t="n">
         <v>-6086.26</v>
       </c>
-      <c r="AF15" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2166,9 +2118,6 @@
       <c r="AE16" s="3" t="n">
         <v>-20000</v>
       </c>
-      <c r="AF16" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2266,9 +2215,6 @@
       <c r="AE17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF17" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2366,9 +2312,6 @@
       <c r="AE18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF18" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2466,9 +2409,6 @@
       <c r="AE19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF19" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2566,9 +2506,6 @@
       <c r="AE20" s="3" t="n">
         <v>-151750</v>
       </c>
-      <c r="AF20" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2666,9 +2603,6 @@
       <c r="AE21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF21" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2766,9 +2700,6 @@
       <c r="AE22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF22" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2866,9 +2797,6 @@
       <c r="AE23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF23" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2966,9 +2894,6 @@
       <c r="AE24" s="3" t="n">
         <v>-10000</v>
       </c>
-      <c r="AF24" s="3" t="n">
-        <v>-20000</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -3066,9 +2991,6 @@
       <c r="AE25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF25" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3166,9 +3088,6 @@
       <c r="AE26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF26" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3266,9 +3185,6 @@
       <c r="AE27" s="3" t="n">
         <v>-26453.74</v>
       </c>
-      <c r="AF27" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3366,9 +3282,6 @@
       <c r="AE28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF28" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3466,9 +3379,6 @@
       <c r="AE29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF29" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3566,9 +3476,6 @@
       <c r="AE30" s="3" t="n">
         <v>-15370</v>
       </c>
-      <c r="AF30" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3666,9 +3573,6 @@
       <c r="AE31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF31" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3766,9 +3670,6 @@
       <c r="AE32" s="3" t="n">
         <v>311700</v>
       </c>
-      <c r="AF32" s="3" t="n">
-        <v>1100</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3866,9 +3767,6 @@
       <c r="AE33" s="5" t="n">
         <v>311700</v>
       </c>
-      <c r="AF33" s="5" t="n">
-        <v>1100</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3966,9 +3864,6 @@
       <c r="AE34" s="5" t="n">
         <v>-339720.91</v>
       </c>
-      <c r="AF34" s="5" t="n">
-        <v>-20000</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -4066,9 +3961,6 @@
       <c r="AE35" s="7" t="n">
         <v>-28020.91</v>
       </c>
-      <c r="AF35" s="7" t="n">
-        <v>-18900</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -4165,9 +4057,6 @@
       </c>
       <c r="AE36" s="5" t="n">
         <v>-118369.68</v>
-      </c>
-      <c r="AF36" s="5" t="n">
-        <v>-137269.68</v>
       </c>
     </row>
   </sheetData>

--- a/Flujo de Efectivo/Flujo de efectivo.xlsx
+++ b/Flujo de Efectivo/Flujo de efectivo.xlsx
@@ -3969,94 +3969,94 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>-943093.17</v>
+        <v>-443093.17</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>-950598.37</v>
+        <v>-450598.37</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>-947598.37</v>
+        <v>-447598.37</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-963018.37</v>
+        <v>-463018.37</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-1047802.37</v>
+        <v>-547802.37</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-1063646.37</v>
+        <v>-563646.37</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>-1087979.04</v>
+        <v>-587979.04</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>-1104446.99</v>
+        <v>-604446.99</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-1115016.59</v>
+        <v>-615016.59</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-1083195.44</v>
+        <v>-583195.4399999999</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-892077.16</v>
+        <v>-392077.16</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>-898100.39</v>
+        <v>-398100.39</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>-794652.39</v>
+        <v>-294652.39</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>-793736.39</v>
+        <v>-293736.39</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>-713557.54</v>
+        <v>-213557.54</v>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>-497545.36</v>
+        <v>2454.64</v>
       </c>
       <c r="R36" s="5" t="n">
-        <v>-499212.96</v>
+        <v>787.04</v>
       </c>
       <c r="S36" s="5" t="n">
-        <v>-405477.16</v>
+        <v>94522.84</v>
       </c>
       <c r="T36" s="5" t="n">
-        <v>-296271.08</v>
+        <v>203728.92</v>
       </c>
       <c r="U36" s="5" t="n">
-        <v>-52791.18</v>
+        <v>447208.82</v>
       </c>
       <c r="V36" s="5" t="n">
-        <v>-69442.09</v>
+        <v>430557.91</v>
       </c>
       <c r="W36" s="5" t="n">
-        <v>-102625.99</v>
+        <v>397374.01</v>
       </c>
       <c r="X36" s="5" t="n">
-        <v>-57181.91</v>
+        <v>442818.09</v>
       </c>
       <c r="Y36" s="5" t="n">
-        <v>35775.04</v>
+        <v>535775.04</v>
       </c>
       <c r="Z36" s="5" t="n">
-        <v>-15199.07</v>
+        <v>484800.93</v>
       </c>
       <c r="AA36" s="5" t="n">
-        <v>-38017.39</v>
+        <v>461982.61</v>
       </c>
       <c r="AB36" s="5" t="n">
-        <v>-46613.43</v>
+        <v>453386.57</v>
       </c>
       <c r="AC36" s="5" t="n">
-        <v>-83374.75</v>
+        <v>416625.25</v>
       </c>
       <c r="AD36" s="5" t="n">
-        <v>-90348.77</v>
+        <v>409651.23</v>
       </c>
       <c r="AE36" s="5" t="n">
-        <v>-118369.68</v>
+        <v>381630.32</v>
       </c>
     </row>
   </sheetData>

--- a/Flujo de Efectivo/Flujo de efectivo.xlsx
+++ b/Flujo de Efectivo/Flujo de efectivo.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="003D5A28"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="13"/>
     </font>
   </fonts>
@@ -46,17 +51,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="003D5A28"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="00EEF3E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009DC3E6"/>
+        <fgColor rgb="005B7F3B"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,16 +94,16 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AF14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -500,6 +505,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="18" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -658,6 +664,11 @@
           <t>25-30 mayo</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>09-14 julio 2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -755,6 +766,9 @@
       <c r="AE2" s="3" t="n">
         <v>-13091.4</v>
       </c>
+      <c r="AF2" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -852,6 +866,9 @@
       <c r="AE3" s="3" t="n">
         <v>-13428</v>
       </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -949,6 +966,9 @@
       <c r="AE4" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AF4" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1046,6 +1066,9 @@
       <c r="AE5" s="3" t="n">
         <v>-85747.77</v>
       </c>
+      <c r="AF5" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1143,6 +1166,9 @@
       <c r="AE6" s="3" t="n">
         <v>-151300</v>
       </c>
+      <c r="AF6" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1240,15 +1266,18 @@
       <c r="AE7" s="3" t="n">
         <v>-49700</v>
       </c>
+      <c r="AF7" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Seguro Social</t>
+          <t>Saldo</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-126280.06</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -1272,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1284,7 +1313,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
@@ -1317,510 +1346,628 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-22329.13</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-20000</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AC8" s="3" t="n">
-        <v>-14685.06</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>-26453.74</v>
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>500000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Ventas</t>
+          <t>Seguro Social</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>-126280.06</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>303500.8</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>295000</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>138000</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>138000</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>447710</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>381000</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>595026.8</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>198000</v>
+        <v>-10000</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>221544.8</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>299468.28</v>
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>165824</v>
+        <v>0</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>321376</v>
+        <v>-30000</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>249424</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>300680</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>437300</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>227100</v>
+        <v>0</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>328790</v>
+        <v>0</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>328790</v>
+        <v>0</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>328790</v>
+        <v>0</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>203456</v>
+        <v>0</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>132880</v>
+        <v>0</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>199760</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>323806.08</v>
+        <v>-22329.13</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>524873.2</v>
+        <v>-20000</v>
       </c>
       <c r="AA9" s="3" t="n">
-        <v>333976</v>
+        <v>-10000</v>
       </c>
       <c r="AB9" s="3" t="n">
-        <v>193267.8</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="3" t="n">
-        <v>353464</v>
+        <v>-14685.06</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>206448</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>311700</v>
+        <v>-26453.74</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL INGRESOS</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="5" t="n">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>303500.8</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="3" t="n">
         <v>295000</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="3" t="n">
         <v>138000</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="3" t="n">
         <v>138000</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="3" t="n">
         <v>447710</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="3" t="n">
         <v>381000</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I10" s="3" t="n">
         <v>595026.8</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J10" s="3" t="n">
         <v>198000</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="K10" s="3" t="n">
         <v>221544.8</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="L10" s="3" t="n">
         <v>299468.28</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="M10" s="3" t="n">
         <v>165824</v>
       </c>
-      <c r="N10" s="5" t="n">
+      <c r="N10" s="3" t="n">
         <v>321376</v>
       </c>
-      <c r="O10" s="5" t="n">
+      <c r="O10" s="3" t="n">
         <v>249424</v>
       </c>
-      <c r="P10" s="5" t="n">
+      <c r="P10" s="3" t="n">
         <v>300680</v>
       </c>
-      <c r="Q10" s="5" t="n">
+      <c r="Q10" s="3" t="n">
         <v>437300</v>
       </c>
-      <c r="R10" s="5" t="n">
+      <c r="R10" s="3" t="n">
         <v>227100</v>
       </c>
-      <c r="S10" s="5" t="n">
+      <c r="S10" s="3" t="n">
         <v>328790</v>
       </c>
-      <c r="T10" s="5" t="n">
+      <c r="T10" s="3" t="n">
         <v>328790</v>
       </c>
-      <c r="U10" s="5" t="n">
+      <c r="U10" s="3" t="n">
         <v>328790</v>
       </c>
-      <c r="V10" s="5" t="n">
+      <c r="V10" s="3" t="n">
         <v>203456</v>
       </c>
-      <c r="W10" s="5" t="n">
+      <c r="W10" s="3" t="n">
         <v>132880</v>
       </c>
-      <c r="X10" s="5" t="n">
+      <c r="X10" s="3" t="n">
         <v>199760</v>
       </c>
-      <c r="Y10" s="5" t="n">
+      <c r="Y10" s="3" t="n">
         <v>323806.08</v>
       </c>
-      <c r="Z10" s="5" t="n">
+      <c r="Z10" s="3" t="n">
         <v>524873.2</v>
       </c>
-      <c r="AA10" s="5" t="n">
+      <c r="AA10" s="3" t="n">
         <v>333976</v>
       </c>
-      <c r="AB10" s="5" t="n">
+      <c r="AB10" s="3" t="n">
         <v>193267.8</v>
       </c>
-      <c r="AC10" s="5" t="n">
+      <c r="AC10" s="3" t="n">
         <v>353464</v>
       </c>
-      <c r="AD10" s="5" t="n">
+      <c r="AD10" s="3" t="n">
         <v>206448</v>
       </c>
-      <c r="AE10" s="5" t="n">
+      <c r="AE10" s="3" t="n">
         <v>311700</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>TOTAL EGRESOS</t>
+          <t>TOTAL INGRESOS</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>-943093.17</v>
+        <v>0</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-311006</v>
+        <v>303500.8</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-292000</v>
+        <v>295000</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-153420</v>
+        <v>138000</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-222784</v>
+        <v>138000</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-463554</v>
+        <v>447710</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-405332.67</v>
+        <v>381000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>-611494.75</v>
+        <v>595026.8</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-208569.6</v>
+        <v>198000</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>-189723.65</v>
+        <v>221544.8</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-108350</v>
+        <v>299468.28</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>-171847.23</v>
+        <v>165824</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>-217928</v>
+        <v>321376</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>-248508</v>
+        <v>249424</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-220501.15</v>
+        <v>300680</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>-221287.82</v>
+        <v>437300</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>-228767.6</v>
+        <v>227100</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>-235054.2</v>
+        <v>328790</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>-219583.92</v>
+        <v>328790</v>
       </c>
       <c r="U11" s="5" t="n">
-        <v>-85310.10000000001</v>
+        <v>328790</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>-220106.91</v>
+        <v>203456</v>
       </c>
       <c r="W11" s="5" t="n">
-        <v>-166063.9</v>
+        <v>132880</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>-154315.92</v>
+        <v>199760</v>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>-230849.13</v>
+        <v>323806.08</v>
       </c>
       <c r="Z11" s="5" t="n">
-        <v>-575847.3100000001</v>
+        <v>524873.2</v>
       </c>
       <c r="AA11" s="5" t="n">
-        <v>-356794.32</v>
+        <v>333976</v>
       </c>
       <c r="AB11" s="5" t="n">
-        <v>-201863.84</v>
+        <v>193267.8</v>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>-390225.32</v>
+        <v>353464</v>
       </c>
       <c r="AD11" s="5" t="n">
-        <v>-213422.02</v>
+        <v>206448</v>
       </c>
       <c r="AE11" s="5" t="n">
-        <v>-339720.91</v>
+        <v>311700</v>
+      </c>
+      <c r="AF11" s="5" t="n">
+        <v>500000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>FLUJO NETO</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL EGRESOS</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
         <v>-943093.17</v>
       </c>
-      <c r="C12" s="7" t="n">
-        <v>-7505.2</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>-15420</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>-84784</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>-15844</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>-24332.67</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>-16467.95</v>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>-10569.6</v>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>31821.15</v>
-      </c>
-      <c r="L12" s="7" t="n">
-        <v>191118.28</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>-6023.23</v>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>103448</v>
-      </c>
-      <c r="O12" s="7" t="n">
-        <v>916</v>
-      </c>
-      <c r="P12" s="7" t="n">
-        <v>80178.85000000001</v>
-      </c>
-      <c r="Q12" s="7" t="n">
-        <v>216012.18</v>
-      </c>
-      <c r="R12" s="7" t="n">
-        <v>-1667.6</v>
-      </c>
-      <c r="S12" s="7" t="n">
-        <v>93735.8</v>
-      </c>
-      <c r="T12" s="7" t="n">
-        <v>109206.08</v>
-      </c>
-      <c r="U12" s="7" t="n">
-        <v>243479.9</v>
-      </c>
-      <c r="V12" s="7" t="n">
-        <v>-16650.91</v>
-      </c>
-      <c r="W12" s="7" t="n">
-        <v>-33183.9</v>
-      </c>
-      <c r="X12" s="7" t="n">
-        <v>45444.08</v>
-      </c>
-      <c r="Y12" s="7" t="n">
-        <v>92956.95</v>
-      </c>
-      <c r="Z12" s="7" t="n">
-        <v>-50974.11</v>
-      </c>
-      <c r="AA12" s="7" t="n">
-        <v>-22818.32</v>
-      </c>
-      <c r="AB12" s="7" t="n">
-        <v>-8596.040000000001</v>
-      </c>
-      <c r="AC12" s="7" t="n">
-        <v>-36761.32</v>
-      </c>
-      <c r="AD12" s="7" t="n">
-        <v>-6974.02</v>
-      </c>
-      <c r="AE12" s="7" t="n">
-        <v>-28020.91</v>
+      <c r="C12" s="5" t="n">
+        <v>-311006</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-292000</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-153420</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-222784</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-463554</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-405332.67</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>-611494.75</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>-208569.6</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>-189723.65</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>-108350</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>-171847.23</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>-217928</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>-248508</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>-220501.15</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>-221287.82</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>-228767.6</v>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>-235054.2</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>-219583.92</v>
+      </c>
+      <c r="U12" s="5" t="n">
+        <v>-85310.10000000001</v>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>-220106.91</v>
+      </c>
+      <c r="W12" s="5" t="n">
+        <v>-166063.9</v>
+      </c>
+      <c r="X12" s="5" t="n">
+        <v>-154315.92</v>
+      </c>
+      <c r="Y12" s="5" t="n">
+        <v>-230849.13</v>
+      </c>
+      <c r="Z12" s="5" t="n">
+        <v>-575847.3100000001</v>
+      </c>
+      <c r="AA12" s="5" t="n">
+        <v>-356794.32</v>
+      </c>
+      <c r="AB12" s="5" t="n">
+        <v>-201863.84</v>
+      </c>
+      <c r="AC12" s="5" t="n">
+        <v>-390225.32</v>
+      </c>
+      <c r="AD12" s="5" t="n">
+        <v>-213422.02</v>
+      </c>
+      <c r="AE12" s="5" t="n">
+        <v>-339720.91</v>
+      </c>
+      <c r="AF12" s="5" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>FLUJO NETO</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>-943093.17</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>-7505.2</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>-15420</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>-84784</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>-15844</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>-24332.67</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>-16467.95</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>-10569.6</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>31821.15</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>191118.28</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>-6023.23</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>103448</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>916</v>
+      </c>
+      <c r="P13" s="7" t="n">
+        <v>80178.85000000001</v>
+      </c>
+      <c r="Q13" s="7" t="n">
+        <v>216012.18</v>
+      </c>
+      <c r="R13" s="7" t="n">
+        <v>-1667.6</v>
+      </c>
+      <c r="S13" s="7" t="n">
+        <v>93735.8</v>
+      </c>
+      <c r="T13" s="7" t="n">
+        <v>109206.08</v>
+      </c>
+      <c r="U13" s="7" t="n">
+        <v>243479.9</v>
+      </c>
+      <c r="V13" s="7" t="n">
+        <v>-16650.91</v>
+      </c>
+      <c r="W13" s="7" t="n">
+        <v>-33183.9</v>
+      </c>
+      <c r="X13" s="7" t="n">
+        <v>45444.08</v>
+      </c>
+      <c r="Y13" s="7" t="n">
+        <v>92956.95</v>
+      </c>
+      <c r="Z13" s="7" t="n">
+        <v>-50974.11</v>
+      </c>
+      <c r="AA13" s="7" t="n">
+        <v>-22818.32</v>
+      </c>
+      <c r="AB13" s="7" t="n">
+        <v>-8596.040000000001</v>
+      </c>
+      <c r="AC13" s="7" t="n">
+        <v>-36761.32</v>
+      </c>
+      <c r="AD13" s="7" t="n">
+        <v>-6974.02</v>
+      </c>
+      <c r="AE13" s="7" t="n">
+        <v>-28020.91</v>
+      </c>
+      <c r="AF13" s="7" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SALDO</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>56906.83</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>49401.63</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>52401.63</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>36981.63</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>-47802.37</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>-63646.37</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>-87979.03999999999</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>-104446.99</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>-115016.59</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>-83195.44</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>107922.84</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>101899.61</v>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>205347.61</v>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v>206263.61</v>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>286442.46</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>502454.64</v>
-      </c>
-      <c r="R13" s="5" t="n">
-        <v>500787.04</v>
-      </c>
-      <c r="S13" s="5" t="n">
-        <v>594522.84</v>
-      </c>
-      <c r="T13" s="5" t="n">
-        <v>703728.92</v>
-      </c>
-      <c r="U13" s="5" t="n">
-        <v>947208.8199999999</v>
-      </c>
-      <c r="V13" s="5" t="n">
-        <v>930557.91</v>
-      </c>
-      <c r="W13" s="5" t="n">
-        <v>897374.01</v>
-      </c>
-      <c r="X13" s="5" t="n">
-        <v>942818.09</v>
-      </c>
-      <c r="Y13" s="5" t="n">
-        <v>1035775.04</v>
-      </c>
-      <c r="Z13" s="5" t="n">
-        <v>984800.9300000001</v>
-      </c>
-      <c r="AA13" s="5" t="n">
-        <v>961982.61</v>
-      </c>
-      <c r="AB13" s="5" t="n">
-        <v>953386.5699999999</v>
-      </c>
-      <c r="AC13" s="5" t="n">
-        <v>916625.25</v>
-      </c>
-      <c r="AD13" s="5" t="n">
-        <v>909651.23</v>
-      </c>
-      <c r="AE13" s="5" t="n">
-        <v>881630.3199999999</v>
+      <c r="B14" s="5" t="n">
+        <v>-943093.17</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-950598.37</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-947598.37</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-963018.37</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1047802.37</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>-1063646.37</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>-1087979.04</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>-1104446.99</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>-1115016.59</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>-1083195.44</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>-892077.16</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>-898100.39</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>-794652.39</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>-793736.39</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>-713557.54</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>-497545.36</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>-499212.96</v>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>-405477.16</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>-296271.08</v>
+      </c>
+      <c r="U14" s="5" t="n">
+        <v>-52791.18</v>
+      </c>
+      <c r="V14" s="5" t="n">
+        <v>-69442.09</v>
+      </c>
+      <c r="W14" s="5" t="n">
+        <v>-102625.99</v>
+      </c>
+      <c r="X14" s="5" t="n">
+        <v>-57181.91</v>
+      </c>
+      <c r="Y14" s="5" t="n">
+        <v>35775.04</v>
+      </c>
+      <c r="Z14" s="5" t="n">
+        <v>-15199.07</v>
+      </c>
+      <c r="AA14" s="5" t="n">
+        <v>-38017.39</v>
+      </c>
+      <c r="AB14" s="5" t="n">
+        <v>-46613.43</v>
+      </c>
+      <c r="AC14" s="5" t="n">
+        <v>-83374.75</v>
+      </c>
+      <c r="AD14" s="5" t="n">
+        <v>-90348.77</v>
+      </c>
+      <c r="AE14" s="5" t="n">
+        <v>-118369.68</v>
+      </c>
+      <c r="AF14" s="5" t="n">
+        <v>381630.32</v>
       </c>
     </row>
   </sheetData>
